--- a/AtchisonRegime/Outputs/USA/USA500_Utilities/df_regEquityReturns_USA500_Utilities.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500_Utilities/df_regEquityReturns_USA500_Utilities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q161"/>
+  <dimension ref="A1:Q162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9022,7 +9022,7 @@
         <v>-1.113652454430497</v>
       </c>
       <c r="C151" t="n">
-        <v>0.006266379198084816</v>
+        <v>-0.01570867082860625</v>
       </c>
       <c r="D151" t="b">
         <v>0</v>
@@ -9079,7 +9079,7 @@
         <v>-1.13653593688915</v>
       </c>
       <c r="C152" t="n">
-        <v>0.02240605369896704</v>
+        <v>0.005131485533573125</v>
       </c>
       <c r="D152" t="b">
         <v>0</v>
@@ -9136,7 +9136,7 @@
         <v>-1.151360964367</v>
       </c>
       <c r="C153" t="n">
-        <v>0.05890779434252914</v>
+        <v>0.04460226520446691</v>
       </c>
       <c r="D153" t="b">
         <v>0</v>
@@ -9193,7 +9193,7 @@
         <v>-1.199054339561413</v>
       </c>
       <c r="C154" t="n">
-        <v>0.1365357185829741</v>
+        <v>0.10691331821946</v>
       </c>
       <c r="D154" t="b">
         <v>0</v>
@@ -9250,7 +9250,7 @@
         <v>-1.211312601852137</v>
       </c>
       <c r="C155" t="n">
-        <v>0.19626538484902</v>
+        <v>0.1742576329953394</v>
       </c>
       <c r="D155" t="b">
         <v>0</v>
@@ -9307,7 +9307,7 @@
         <v>-1.189056899431358</v>
       </c>
       <c r="C156" t="n">
-        <v>0.2479141243562677</v>
+        <v>0.2230893786343014</v>
       </c>
       <c r="D156" t="b">
         <v>0</v>
@@ -9364,7 +9364,7 @@
         <v>-1.098247223033612</v>
       </c>
       <c r="C157" t="n">
-        <v>0.2597235153389927</v>
+        <v>0.2419933628466199</v>
       </c>
       <c r="D157" t="b">
         <v>0</v>
@@ -9421,7 +9421,7 @@
         <v>-0.9817076186491491</v>
       </c>
       <c r="C158" t="n">
-        <v>0.2098083315261438</v>
+        <v>0.2090047006632499</v>
       </c>
       <c r="D158" t="b">
         <v>0</v>
@@ -9478,7 +9478,7 @@
         <v>-0.8763018590939128</v>
       </c>
       <c r="C159" t="n">
-        <v>0.1536160686024298</v>
+        <v>0.1277646818410845</v>
       </c>
       <c r="D159" t="b">
         <v>0</v>
@@ -9532,10 +9532,10 @@
         <v>45716</v>
       </c>
       <c r="B160" t="n">
-        <v>-0.8167702922088305</v>
+        <v>-0.8165764810113098</v>
       </c>
       <c r="C160" t="n">
-        <v>0.04657800836005581</v>
+        <v>0.03018097094312175</v>
       </c>
       <c r="D160" t="b">
         <v>0</v>
@@ -9589,10 +9589,10 @@
         <v>45747</v>
       </c>
       <c r="B161" t="n">
-        <v>-0.7844280456827043</v>
+        <v>-0.836774216411349</v>
       </c>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>-0.04969816765883398</v>
       </c>
       <c r="D161" t="b">
         <v>0</v>
@@ -9639,6 +9639,63 @@
       </c>
       <c r="Q161" t="n">
         <v>204.1190817544306</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B162" t="n">
+        <v>-0.879407738343786</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.07980487945422567</v>
+      </c>
+      <c r="D162" t="b">
+        <v>0</v>
+      </c>
+      <c r="E162" t="b">
+        <v>1</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1.84422143695207</v>
+      </c>
+      <c r="G162" t="n">
+        <v>526030.3893879529</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>1.84422143695207</v>
+      </c>
+      <c r="N162" t="n">
+        <v>118.512512876337</v>
+      </c>
+      <c r="O162" t="n">
+        <v>130.1738433328881</v>
+      </c>
+      <c r="P162" t="n">
+        <v>158.5034298398725</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>207.8834896170555</v>
       </c>
     </row>
   </sheetData>
